--- a/RevGame_Client/配置表/关卡与奖励配置.xlsx
+++ b/RevGame_Client/配置表/关卡与奖励配置.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyReinforceConfig" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardConfig" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardBoostConfig" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkillConfig" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1372,6 +1373,573 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Hint</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>UnlockChapter</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Cooldown</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Windup</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Interval</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>技能编号，必须与代码枚举 BossSkillKind 同名；每个枚举恰好一行</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>技能中文名：HUD 弹幕标题与战报使用</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>给玩家的应对提示：HUD 弹幕副标题使用，建议说清“躲哪里”</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>从第几章开始 Boss 会使用该技能（1~6）。第六章 Boss 拥有全部技能</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>选技能时的基础权重；0 表示不参与随机挑选（只能由条件触发，例如狂暴）</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>该技能两次使用之间的冷却（秒，第1章基准；章节越高按 Boss.CooldownPerChapter 缩短）</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>蓄力预警时长（秒）：期间画出危险区域，玩家可以把棋子移开</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>多段技能每段之间的间隔（秒）；单段技能填 0</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>段数/数量：轰炸=炸弹数，激光=伤害段数，汲取=目标数，召唤=召唤数，弹幕=子弹数（只结算一次伤害）</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>伤害倍率：相对 Boss 一次普通攻击的伤害；0 表示不造成伤害</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>伤害半径（格）：0 表示单体</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Cleave</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>横扫震地</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Boss 身边一圈即将受击，快把棋子散开</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Snipe</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>致命狙击</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>红色准星锁定了一颗棋子，把它移出射线</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Bombard</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>三连轰炸</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>远处区域将依次落下三发炸弹</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>BulletRing</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>弹幕风暴</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>以 Boss 为圆心向外扫射一圈弹幕</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>BlinkBlast</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>瞬影爆破</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Boss 将瞬移到阵中空位并爆炸</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>LaserSpin</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>天光回旋</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>激光环绕 Boss 旋转，造成三段伤害</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>SoulDrain</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>灵魂汲取</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>残血棋子将被吸走生命，Boss 随之回血</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>召唤影卫</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Boss 召唤影卫增援，先清理它们</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Enrage</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>狂暴怒吼</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Boss 狂暴：此后技能冷却大幅缩短</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/RevGame_Client/配置表/关卡与奖励配置.xlsx
+++ b/RevGame_Client/配置表/关卡与奖励配置.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChapterConfig" sheetId="1" r:id="R2d82066df88e48a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyRosterConfig" sheetId="2" r:id="R88ab6481c08b4bf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyReinforceConfig" sheetId="3" r:id="R4dbd252dbe3245d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardConfig" sheetId="4" r:id="R6ed59d4664984a84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardBoostConfig" sheetId="5" r:id="Rdf3ed93a26f84b6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkillConfig" sheetId="6" r:id="R7ba09d7db8f04008"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="7" r:id="R436efcd8a439416b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChapterConfig" sheetId="1" r:id="Rbeaad6bc68e74788"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyRosterConfig" sheetId="2" r:id="Rdc7f92f404ff423f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyReinforceConfig" sheetId="3" r:id="R7b3775aec3194264"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardConfig" sheetId="4" r:id="R5da2bca4856f4b41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardBoostConfig" sheetId="5" r:id="Rdbd5eaa3d0314179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkillConfig" sheetId="6" r:id="R06ed19a7aa8f437d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="7" r:id="R06a1851ba327401a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -441,7 +441,7 @@
         <x:v>本章 Boss 大棋的星级（1~3）</x:v>
       </x:c>
       <x:c r="E3" t="str">
-        <x:v>本章 Boss 大棋占格边长，逗号分隔，第一颗是带王冠的主将（如 3,2,2 表示三颗大棋）；每项 1~3</x:v>
+        <x:v>本章唯一Boss的占格边长，仅填写2或3；禁止逗号和多Boss阵容</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -492,7 +492,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" t="str">
-        <x:v>2,2</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -509,7 +509,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E7" t="str">
-        <x:v>2,2</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -526,7 +526,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E8" t="str">
-        <x:v>3,2,2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -543,7 +543,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E9" t="str">
-        <x:v>3,3</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/RevGame_Client/配置表/关卡与奖励配置.xlsx
+++ b/RevGame_Client/配置表/关卡与奖励配置.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChapterConfig" sheetId="1" r:id="Rbeaad6bc68e74788"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyRosterConfig" sheetId="2" r:id="Rdc7f92f404ff423f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyReinforceConfig" sheetId="3" r:id="R7b3775aec3194264"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardConfig" sheetId="4" r:id="R5da2bca4856f4b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardBoostConfig" sheetId="5" r:id="Rdbd5eaa3d0314179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkillConfig" sheetId="6" r:id="R06ed19a7aa8f437d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="7" r:id="R06a1851ba327401a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChapterConfig" sheetId="1" r:id="R09a687b61f464ca3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyRosterConfig" sheetId="2" r:id="R4e1192592f374461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyReinforceConfig" sheetId="3" r:id="Re980b777efe54952"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardConfig" sheetId="4" r:id="Rd8a5f6294f6e442b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardBoostConfig" sheetId="5" r:id="R90b17f4426274240"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkillConfig" sheetId="6" r:id="Rb9899ce9cece43a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="7" r:id="R8c4c1d9cad7b4931"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -454,8 +454,8 @@
       <x:c r="C4" t="str">
         <x:v>HeavySword</x:v>
       </x:c>
-      <x:c r="D4" t="str">
-        <x:v>3</x:v>
+      <x:c r="D4" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E4" t="str">
         <x:v>2</x:v>
@@ -471,8 +471,8 @@
       <x:c r="C5" t="str">
         <x:v>HeavySword</x:v>
       </x:c>
-      <x:c r="D5" t="str">
-        <x:v>3</x:v>
+      <x:c r="D5" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E5" t="str">
         <x:v>2</x:v>
@@ -482,14 +482,14 @@
       <x:c r="A6" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" t="str">
-        <x:v>2</x:v>
+      <x:c r="B6" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" t="str">
         <x:v>HeavySword</x:v>
       </x:c>
-      <x:c r="D6" t="str">
-        <x:v>3</x:v>
+      <x:c r="D6" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E6" t="str">
         <x:v>2</x:v>
@@ -499,14 +499,14 @@
       <x:c r="A7" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" t="str">
-        <x:v>2</x:v>
+      <x:c r="B7" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C7" t="str">
         <x:v>HeavySword</x:v>
       </x:c>
-      <x:c r="D7" t="str">
-        <x:v>3</x:v>
+      <x:c r="D7" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E7" t="str">
         <x:v>2</x:v>
@@ -516,14 +516,14 @@
       <x:c r="A8" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B8" t="str">
-        <x:v>3</x:v>
+      <x:c r="B8" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" t="str">
         <x:v>HeavySword</x:v>
       </x:c>
-      <x:c r="D8" t="str">
-        <x:v>3</x:v>
+      <x:c r="D8" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E8" t="str">
         <x:v>3</x:v>
@@ -533,14 +533,14 @@
       <x:c r="A9" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B9" t="str">
-        <x:v>3</x:v>
+      <x:c r="B9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" t="str">
         <x:v>HeavySword</x:v>
       </x:c>
-      <x:c r="D9" t="str">
-        <x:v>3</x:v>
+      <x:c r="D9" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E9" t="str">
         <x:v>3</x:v>
@@ -628,7 +628,7 @@
         <x:v>Filler</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>Shield</x:v>
+        <x:v>Archer</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -639,7 +639,7 @@
         <x:v>Filler</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>HeavySword</x:v>
+        <x:v>MageFire</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -974,8 +974,8 @@
       <x:c r="B4" t="str">
         <x:v>攻击永久 +{Amount%}</x:v>
       </x:c>
-      <x:c r="C4" t="str">
-        <x:v>0.1</x:v>
+      <x:c r="C4" t="n">
+        <x:v>0.06</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -985,8 +985,8 @@
       <x:c r="B5" t="str">
         <x:v>攻速永久 +{Amount%}</x:v>
       </x:c>
-      <x:c r="C5" t="str">
-        <x:v>0.1</x:v>
+      <x:c r="C5" t="n">
+        <x:v>0.06</x:v>
       </x:c>
     </x:row>
     <x:row r="6">

--- a/RevGame_Client/配置表/关卡与奖励配置.xlsx
+++ b/RevGame_Client/配置表/关卡与奖励配置.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChapterConfig" sheetId="1" r:id="R09a687b61f464ca3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyRosterConfig" sheetId="2" r:id="R4e1192592f374461"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyReinforceConfig" sheetId="3" r:id="Re980b777efe54952"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardConfig" sheetId="4" r:id="Rd8a5f6294f6e442b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardBoostConfig" sheetId="5" r:id="R90b17f4426274240"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkillConfig" sheetId="6" r:id="Rb9899ce9cece43a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="7" r:id="R8c4c1d9cad7b4931"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChapterConfig" sheetId="1" r:id="R2b2fd29113b246c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyRosterConfig" sheetId="2" r:id="R3b98d5d7d52b48bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyReinforceConfig" sheetId="3" r:id="Rdc2648f742174a7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardConfig" sheetId="4" r:id="R9b9eae6f933e427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardBoostConfig" sheetId="5" r:id="Ra29bf49945ea4387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkillConfig" sheetId="6" r:id="Rab54698790e14960"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="7" r:id="Rc56fabe9b8554376"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1007,6 +1007,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:cols>
+    <x:col min="13" max="13" width="19" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="19" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="19" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="19" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" t="str">
@@ -1045,6 +1051,18 @@
       <x:c r="L1" t="str">
         <x:v>BulletSpeed</x:v>
       </x:c>
+      <x:c r="M1" t="str">
+        <x:v>ExclusiveChapter</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>Duration</x:v>
+      </x:c>
+      <x:c r="O1" t="str">
+        <x:v>AttackFactor</x:v>
+      </x:c>
+      <x:c r="P1" t="str">
+        <x:v>SpeedFactor</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
@@ -1083,6 +1101,18 @@
       <x:c r="L2" t="str">
         <x:v>float</x:v>
       </x:c>
+      <x:c r="M2" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="O2" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="P2" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
@@ -1095,7 +1125,7 @@
         <x:v>给玩家的应对提示：HUD 弹幕副标题使用，建议说清“躲哪里”</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>从第几章开始 Boss 会使用该技能（1~6）。第六章 Boss 拥有全部技能</x:v>
+        <x:v>最低解锁章；专属技能还须匹配ExclusiveChapter</x:v>
       </x:c>
       <x:c r="E3" t="str">
         <x:v>选技能时的基础权重；0 表示不参与随机挑选（只能由条件触发，例如狂暴）</x:v>
@@ -1120,6 +1150,18 @@
       </x:c>
       <x:c r="L3" t="str">
         <x:v>弹幕飞行速度（格/秒）：只有弹幕类技能使用，0 表示该技能不发射飞行弹幕。数值越小飞得越慢、越容易看清与躲避；它只决定表现快慢，不改变伤害与命中判定</x:v>
+      </x:c>
+      <x:c r="M3" t="str">
+        <x:v>0为通用；1至6仅本章使用</x:v>
+      </x:c>
+      <x:c r="N3" t="str">
+        <x:v>控制/区域持续秒数，0表示无持续状态</x:v>
+      </x:c>
+      <x:c r="O3" t="str">
+        <x:v>状态期间攻击倍率（0至1）</x:v>
+      </x:c>
+      <x:c r="P3" t="str">
+        <x:v>状态期间攻速倍率（0至1）</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1132,7 +1174,7 @@
       <x:c r="C4" t="str">
         <x:v>Boss 身边一圈即将受击，快把棋子散开</x:v>
       </x:c>
-      <x:c r="D4" t="str">
+      <x:c r="D4" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" t="str">
@@ -1158,6 +1200,18 @@
       </x:c>
       <x:c r="L4" t="str">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O4" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P4" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1170,7 +1224,7 @@
       <x:c r="C5" t="str">
         <x:v>红色准星锁定了一颗棋子，把它移出射线</x:v>
       </x:c>
-      <x:c r="D5" t="str">
+      <x:c r="D5" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E5" t="str">
@@ -1196,6 +1250,18 @@
       </x:c>
       <x:c r="L5" t="str">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P5" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1208,8 +1274,8 @@
       <x:c r="C6" t="str">
         <x:v>远处区域将依次落下三发炸弹</x:v>
       </x:c>
-      <x:c r="D6" t="str">
-        <x:v>2</x:v>
+      <x:c r="D6" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E6" t="str">
         <x:v>25</x:v>
@@ -1234,6 +1300,18 @@
       </x:c>
       <x:c r="L6" t="str">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P6" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1246,8 +1324,8 @@
       <x:c r="C7" t="str">
         <x:v>以 Boss 自身为中心生成一圈子弹同时向全屏散射，无距离限制</x:v>
       </x:c>
-      <x:c r="D7" t="str">
-        <x:v>3</x:v>
+      <x:c r="D7" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E7" t="str">
         <x:v>20</x:v>
@@ -1272,6 +1350,18 @@
       </x:c>
       <x:c r="L7" t="str">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="M7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P7" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1284,8 +1374,8 @@
       <x:c r="C8" t="str">
         <x:v>Boss 将瞬移到阵中空位并爆炸</x:v>
       </x:c>
-      <x:c r="D8" t="str">
-        <x:v>4</x:v>
+      <x:c r="D8" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E8" t="str">
         <x:v>20</x:v>
@@ -1310,6 +1400,18 @@
       </x:c>
       <x:c r="L8" t="str">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P8" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1322,8 +1424,8 @@
       <x:c r="C9" t="str">
         <x:v>激光环绕 Boss 旋转，造成三段伤害</x:v>
       </x:c>
-      <x:c r="D9" t="str">
-        <x:v>5</x:v>
+      <x:c r="D9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E9" t="str">
         <x:v>18</x:v>
@@ -1348,6 +1450,18 @@
       </x:c>
       <x:c r="L9" t="str">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P9" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1360,8 +1474,8 @@
       <x:c r="C10" t="str">
         <x:v>残血棋子将被吸走生命，Boss 随之回血</x:v>
       </x:c>
-      <x:c r="D10" t="str">
-        <x:v>5</x:v>
+      <x:c r="D10" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E10" t="str">
         <x:v>15</x:v>
@@ -1386,6 +1500,18 @@
       </x:c>
       <x:c r="L10" t="str">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P10" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1398,8 +1524,8 @@
       <x:c r="C11" t="str">
         <x:v>Boss 召唤影卫增援，先清理它们</x:v>
       </x:c>
-      <x:c r="D11" t="str">
-        <x:v>6</x:v>
+      <x:c r="D11" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E11" t="str">
         <x:v>12</x:v>
@@ -1424,6 +1550,18 @@
       </x:c>
       <x:c r="L11" t="str">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P11" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1436,8 +1574,8 @@
       <x:c r="C12" t="str">
         <x:v>Boss 狂暴：此后技能冷却大幅缩短</x:v>
       </x:c>
-      <x:c r="D12" t="str">
-        <x:v>4</x:v>
+      <x:c r="D12" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E12" t="str">
         <x:v>0</x:v>
@@ -1462,6 +1600,18 @@
       </x:c>
       <x:c r="L12" t="str">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P12" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1475,7 +1625,7 @@
         <x:v>看清三枚落点，移开棋子</x:v>
       </x:c>
       <x:c r="D13" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E13" t="n">
         <x:v>7</x:v>
@@ -1500,6 +1650,18 @@
       </x:c>
       <x:c r="L13" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P13" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1513,7 +1675,7 @@
         <x:v>避开主将横纵轴线</x:v>
       </x:c>
       <x:c r="D14" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E14" t="n">
         <x:v>6</x:v>
@@ -1538,6 +1700,18 @@
       </x:c>
       <x:c r="L14" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P14" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1551,7 +1725,7 @@
         <x:v>冰环逐圈外扩，离开预警圈</x:v>
       </x:c>
       <x:c r="D15" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E15" t="n">
         <x:v>7</x:v>
@@ -1576,6 +1750,18 @@
       </x:c>
       <x:c r="L15" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P15" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1589,7 +1775,7 @@
         <x:v>雷电依次跳向锁定目标格</x:v>
       </x:c>
       <x:c r="D16" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E16" t="n">
         <x:v>7</x:v>
@@ -1614,6 +1800,18 @@
       </x:c>
       <x:c r="L16" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P16" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1627,7 +1825,7 @@
         <x:v>毒池持续三段，及时离开</x:v>
       </x:c>
       <x:c r="D17" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E17" t="n">
         <x:v>6</x:v>
@@ -1652,6 +1850,18 @@
       </x:c>
       <x:c r="L17" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P17" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1665,7 +1875,7 @@
         <x:v>离开红色纵列火墙</x:v>
       </x:c>
       <x:c r="D18" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E18" t="n">
         <x:v>7</x:v>
@@ -1690,6 +1900,18 @@
       </x:c>
       <x:c r="L18" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P18" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1703,7 +1925,7 @@
         <x:v>避开蓝色横排冰刺</x:v>
       </x:c>
       <x:c r="D19" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E19" t="n">
         <x:v>7</x:v>
@@ -1728,6 +1950,18 @@
       </x:c>
       <x:c r="L19" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P19" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1741,7 +1975,7 @@
         <x:v>紫色引力场逐步向中心收缩</x:v>
       </x:c>
       <x:c r="D20" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E20" t="n">
         <x:v>8</x:v>
@@ -1766,6 +2000,18 @@
       </x:c>
       <x:c r="L20" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P20" t="n">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1779,7 +2025,7 @@
         <x:v>离开金色对角符文，最终中心爆发</x:v>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E21" t="n">
         <x:v>8</x:v>
@@ -1804,6 +2050,618 @@
       </x:c>
       <x:c r="L21" t="n">
         <x:v>0</x:v>
+      </x:c>
+      <x:c r="M21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>StarStorm</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>星辰风暴</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>中央星暴逐圈扩散，避开即将亮起的星环</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F22" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G22" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H22" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="I22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J22" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>BlackHole</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>黑洞陷落</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>眼阵被黑洞吞入，四秒后原位浮出</x:v>
+      </x:c>
+      <x:c r="D23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E23" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F23" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G23" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="H23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J23" t="n">
+        <x:v>0.18</x:v>
+      </x:c>
+      <x:c r="K23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N23" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P23" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>SolarFlare</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>日冕灼潮</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>日冕在锁定区域爆发，余焰持续灼烧</x:v>
+      </x:c>
+      <x:c r="D24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E24" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F24" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G24" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="K24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M24" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N24" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P24" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>SunBrand</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>烈阳烙印</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>三枚太阳烙印灼烧目标，移开标记格</x:v>
+      </x:c>
+      <x:c r="D25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E25" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F25" t="n">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G25" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="H25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I25" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J25" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M25" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N25" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P25" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>TidalSurge</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>怒涛横卷</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>潮墙横扫一排，将棋子冲向侧方空格</x:v>
+      </x:c>
+      <x:c r="D26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E26" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F26" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G26" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H26" t="n">
+        <x:v>0.6</x:v>
+      </x:c>
+      <x:c r="I26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J26" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="K26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M26" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>Maelstrom</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>回流涡旋</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>旋流打乱中心阵型，远离旋涡区域</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E27" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F27" t="n">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G27" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H27" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J27" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K27" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M27" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>SwampMaw</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>沼泽巨口</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>沼泽暂时吞没局部阵型，随后吐回棋盘</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E28" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F28" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G28" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="H28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J28" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N28" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P28" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>MireChains</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>泥沼缚射</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>泥沼缠住区域内远程棋子，离开可解除减速</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E29" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F29" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G29" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J29" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K29" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M29" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N29" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P29" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>FrozenPrison</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>极寒囚笼</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>冰晶冻结区域棋子两秒，期间无法攻击</x:v>
+      </x:c>
+      <x:c r="D30" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E30" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F30" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G30" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="H30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J30" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>GlacialAegis</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>冰封终焉</x:v>
+      </x:c>
+      <x:c r="C31" t="str">
+        <x:v>主将冰封无敌蓄能，冰壳碎裂时全盘爆炸</x:v>
+      </x:c>
+      <x:c r="D31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E31" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F31" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G31" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="H31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J31" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="K31" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="L31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M31" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P31" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>DivineCross</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>十字神罚</x:v>
+      </x:c>
+      <x:c r="C32" t="str">
+        <x:v>金色十字将爆炸，避开横纵交会区域</x:v>
+      </x:c>
+      <x:c r="D32" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E32" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F32" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G32" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J32" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M32" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>Sanctuary</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>圣域</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>离开圣域恢复攻击与攻速，领域消退同时解除</x:v>
+      </x:c>
+      <x:c r="D33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E33" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F33" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G33" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="H33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I33" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J33" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="K33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M33" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N33" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O33" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="P33" t="n">
+        <x:v>0.55</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/RevGame_Client/配置表/关卡与奖励配置.xlsx
+++ b/RevGame_Client/配置表/关卡与奖励配置.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChapterConfig" sheetId="1" r:id="R2b2fd29113b246c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyRosterConfig" sheetId="2" r:id="R3b98d5d7d52b48bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyReinforceConfig" sheetId="3" r:id="Rdc2648f742174a7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardConfig" sheetId="4" r:id="R9b9eae6f933e427f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardBoostConfig" sheetId="5" r:id="Ra29bf49945ea4387"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkillConfig" sheetId="6" r:id="Rab54698790e14960"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="7" r:id="Rc56fabe9b8554376"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChapterConfig" sheetId="1" r:id="R957354ecf36c45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyRosterConfig" sheetId="2" r:id="Ra4dac11a77074d51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EnemyReinforceConfig" sheetId="3" r:id="Rc5492468155c419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardConfig" sheetId="4" r:id="R6f11ad72223e4396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RewardBoostConfig" sheetId="5" r:id="R8f72d3ed638649b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BossSkillConfig" sheetId="6" r:id="R389585f844494d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="7" r:id="R0b4450c71c464f53"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -73,8 +73,11 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="1">
+  <x:cellXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1164,21 +1167,21 @@
         <x:v>状态期间攻速倍率（0至1）</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" t="str">
         <x:v>Cleave</x:v>
       </x:c>
-      <x:c r="B4" t="str">
+      <x:c r="B4" s="1" t="str">
         <x:v>横扫震地</x:v>
       </x:c>
-      <x:c r="C4" t="str">
+      <x:c r="C4" s="1" t="str">
         <x:v>Boss 身边一圈即将受击，快把棋子散开</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E4" t="str">
-        <x:v>30</x:v>
+      <x:c r="E4" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F4" t="str">
         <x:v>6</x:v>
@@ -1214,21 +1217,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="32" customHeight="1">
       <x:c r="A5" t="str">
         <x:v>Snipe</x:v>
       </x:c>
-      <x:c r="B5" t="str">
+      <x:c r="B5" s="1" t="str">
         <x:v>致命狙击</x:v>
       </x:c>
-      <x:c r="C5" t="str">
+      <x:c r="C5" s="1" t="str">
         <x:v>红色准星锁定了一颗棋子，把它移出射线</x:v>
       </x:c>
       <x:c r="D5" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E5" t="str">
-        <x:v>25</x:v>
+      <x:c r="E5" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F5" t="str">
         <x:v>8</x:v>
@@ -1264,21 +1267,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" t="str">
         <x:v>Bombard</x:v>
       </x:c>
-      <x:c r="B6" t="str">
+      <x:c r="B6" s="1" t="str">
         <x:v>三连轰炸</x:v>
       </x:c>
-      <x:c r="C6" t="str">
+      <x:c r="C6" s="1" t="str">
         <x:v>远处区域将依次落下三发炸弹</x:v>
       </x:c>
       <x:c r="D6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>25</x:v>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E6" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" t="str">
         <x:v>9</x:v>
@@ -1314,21 +1317,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" t="str">
         <x:v>BulletRing</x:v>
       </x:c>
-      <x:c r="B7" t="str">
+      <x:c r="B7" s="1" t="str">
         <x:v>弹幕风暴</x:v>
       </x:c>
-      <x:c r="C7" t="str">
+      <x:c r="C7" s="1" t="str">
         <x:v>以 Boss 自身为中心生成一圈子弹同时向全屏散射，无距离限制</x:v>
       </x:c>
       <x:c r="D7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F7" t="str">
         <x:v>10</x:v>
@@ -1364,21 +1367,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="32" customHeight="1">
       <x:c r="A8" t="str">
         <x:v>BlinkBlast</x:v>
       </x:c>
-      <x:c r="B8" t="str">
+      <x:c r="B8" s="1" t="str">
         <x:v>瞬影爆破</x:v>
       </x:c>
-      <x:c r="C8" t="str">
+      <x:c r="C8" s="1" t="str">
         <x:v>Boss 将瞬移到阵中空位并爆炸</x:v>
       </x:c>
       <x:c r="D8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E8" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F8" t="str">
         <x:v>11</x:v>
@@ -1414,21 +1417,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" t="str">
         <x:v>LaserSpin</x:v>
       </x:c>
-      <x:c r="B9" t="str">
+      <x:c r="B9" s="1" t="str">
         <x:v>天光回旋</x:v>
       </x:c>
-      <x:c r="C9" t="str">
+      <x:c r="C9" s="1" t="str">
         <x:v>激光环绕 Boss 旋转，造成三段伤害</x:v>
       </x:c>
       <x:c r="D9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E9" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F9" t="str">
         <x:v>12</x:v>
@@ -1464,20 +1467,20 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" t="str">
         <x:v>SoulDrain</x:v>
       </x:c>
-      <x:c r="B10" t="str">
+      <x:c r="B10" s="1" t="str">
         <x:v>灵魂汲取</x:v>
       </x:c>
-      <x:c r="C10" t="str">
+      <x:c r="C10" s="1" t="str">
         <x:v>残血棋子将被吸走生命，Boss 随之回血</x:v>
       </x:c>
       <x:c r="D10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E10" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F10" t="str">
@@ -1514,21 +1517,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="32" customHeight="1">
       <x:c r="A11" t="str">
         <x:v>Summon</x:v>
       </x:c>
-      <x:c r="B11" t="str">
+      <x:c r="B11" s="1" t="str">
         <x:v>召唤影卫</x:v>
       </x:c>
-      <x:c r="C11" t="str">
+      <x:c r="C11" s="1" t="str">
         <x:v>Boss 召唤影卫增援，先清理它们</x:v>
       </x:c>
       <x:c r="D11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
-        <x:v>12</x:v>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E11" t="n">
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F11" t="str">
         <x:v>16</x:v>
@@ -1564,14 +1567,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="32" customHeight="1">
       <x:c r="A12" t="str">
         <x:v>Enrage</x:v>
       </x:c>
-      <x:c r="B12" t="str">
+      <x:c r="B12" s="1" t="str">
         <x:v>狂暴怒吼</x:v>
       </x:c>
-      <x:c r="C12" t="str">
+      <x:c r="C12" s="1" t="str">
         <x:v>Boss 狂暴：此后技能冷却大幅缩短</x:v>
       </x:c>
       <x:c r="D12" t="n">
@@ -1614,21 +1617,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="32" customHeight="1">
       <x:c r="A13" t="str">
         <x:v>MeteorShower</x:v>
       </x:c>
-      <x:c r="B13" t="str">
+      <x:c r="B13" s="1" t="str">
         <x:v>流星陨落</x:v>
       </x:c>
-      <x:c r="C13" t="str">
+      <x:c r="C13" s="1" t="str">
         <x:v>看清三枚落点，移开棋子</x:v>
       </x:c>
       <x:c r="D13" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E13" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F13" t="n">
         <x:v>18</x:v>
@@ -1664,21 +1667,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" t="str">
         <x:v>CrossLaser</x:v>
       </x:c>
-      <x:c r="B14" t="str">
+      <x:c r="B14" s="1" t="str">
         <x:v>十字天罚</x:v>
       </x:c>
-      <x:c r="C14" t="str">
+      <x:c r="C14" s="1" t="str">
         <x:v>避开主将横纵轴线</x:v>
       </x:c>
       <x:c r="D14" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E14" t="n">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F14" t="n">
         <x:v>16</x:v>
@@ -1714,21 +1717,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" t="str">
         <x:v>FrostNova</x:v>
       </x:c>
-      <x:c r="B15" t="str">
+      <x:c r="B15" s="1" t="str">
         <x:v>极寒新星</x:v>
       </x:c>
-      <x:c r="C15" t="str">
+      <x:c r="C15" s="1" t="str">
         <x:v>冰环逐圈外扩，离开预警圈</x:v>
       </x:c>
       <x:c r="D15" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E15" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F15" t="n">
         <x:v>19</x:v>
@@ -1764,21 +1767,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" t="str">
         <x:v>ChainLightning</x:v>
       </x:c>
-      <x:c r="B16" t="str">
+      <x:c r="B16" s="1" t="str">
         <x:v>连锁雷暴</x:v>
       </x:c>
-      <x:c r="C16" t="str">
+      <x:c r="C16" s="1" t="str">
         <x:v>雷电依次跳向锁定目标格</x:v>
       </x:c>
       <x:c r="D16" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E16" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F16" t="n">
         <x:v>18</x:v>
@@ -1814,21 +1817,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" t="str">
         <x:v>PoisonMarsh</x:v>
       </x:c>
-      <x:c r="B17" t="str">
+      <x:c r="B17" s="1" t="str">
         <x:v>腐蚀毒沼</x:v>
       </x:c>
-      <x:c r="C17" t="str">
+      <x:c r="C17" s="1" t="str">
         <x:v>毒池持续三段，及时离开</x:v>
       </x:c>
       <x:c r="D17" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E17" t="n">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F17" t="n">
         <x:v>22</x:v>
@@ -1864,21 +1867,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="32" customHeight="1">
       <x:c r="A18" t="str">
         <x:v>FlameWall</x:v>
       </x:c>
-      <x:c r="B18" t="str">
+      <x:c r="B18" s="1" t="str">
         <x:v>烈焰火墙</x:v>
       </x:c>
-      <x:c r="C18" t="str">
+      <x:c r="C18" s="1" t="str">
         <x:v>离开红色纵列火墙</x:v>
       </x:c>
       <x:c r="D18" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E18" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F18" t="n">
         <x:v>19</x:v>
@@ -1914,21 +1917,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="32" customHeight="1">
       <x:c r="A19" t="str">
         <x:v>IceLance</x:v>
       </x:c>
-      <x:c r="B19" t="str">
+      <x:c r="B19" s="1" t="str">
         <x:v>冰晶贯穿</x:v>
       </x:c>
-      <x:c r="C19" t="str">
+      <x:c r="C19" s="1" t="str">
         <x:v>避开蓝色横排冰刺</x:v>
       </x:c>
       <x:c r="D19" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E19" t="n">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F19" t="n">
         <x:v>17</x:v>
@@ -1964,21 +1967,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="32" customHeight="1">
       <x:c r="A20" t="str">
         <x:v>GravityWell</x:v>
       </x:c>
-      <x:c r="B20" t="str">
+      <x:c r="B20" s="1" t="str">
         <x:v>引力坍缩</x:v>
       </x:c>
-      <x:c r="C20" t="str">
+      <x:c r="C20" s="1" t="str">
         <x:v>紫色引力场逐步向中心收缩</x:v>
       </x:c>
       <x:c r="D20" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E20" t="n">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F20" t="n">
         <x:v>23</x:v>
@@ -2014,21 +2017,21 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
+    <x:row r="21" ht="32" customHeight="1">
       <x:c r="A21" t="str">
         <x:v>DoomSigil</x:v>
       </x:c>
-      <x:c r="B21" t="str">
+      <x:c r="B21" s="1" t="str">
         <x:v>末日烙印</x:v>
       </x:c>
-      <x:c r="C21" t="str">
+      <x:c r="C21" s="1" t="str">
         <x:v>离开金色对角符文，最终中心爆发</x:v>
       </x:c>
       <x:c r="D21" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E21" t="n">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F21" t="n">
         <x:v>25</x:v>
@@ -2064,14 +2067,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="32" customHeight="1">
       <x:c r="A22" t="str">
         <x:v>StarStorm</x:v>
       </x:c>
-      <x:c r="B22" t="str">
+      <x:c r="B22" s="1" t="str">
         <x:v>星辰风暴</x:v>
       </x:c>
-      <x:c r="C22" t="str">
+      <x:c r="C22" s="1" t="str">
         <x:v>中央星暴逐圈扩散，避开即将亮起的星环</x:v>
       </x:c>
       <x:c r="D22" t="n">
@@ -2114,14 +2117,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
+    <x:row r="23" ht="32" customHeight="1">
       <x:c r="A23" t="str">
         <x:v>BlackHole</x:v>
       </x:c>
-      <x:c r="B23" t="str">
+      <x:c r="B23" s="1" t="str">
         <x:v>黑洞陷落</x:v>
       </x:c>
-      <x:c r="C23" t="str">
+      <x:c r="C23" s="1" t="str">
         <x:v>眼阵被黑洞吞入，四秒后原位浮出</x:v>
       </x:c>
       <x:c r="D23" t="n">
@@ -2164,14 +2167,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="32" customHeight="1">
       <x:c r="A24" t="str">
         <x:v>SolarFlare</x:v>
       </x:c>
-      <x:c r="B24" t="str">
+      <x:c r="B24" s="1" t="str">
         <x:v>日冕灼潮</x:v>
       </x:c>
-      <x:c r="C24" t="str">
+      <x:c r="C24" s="1" t="str">
         <x:v>日冕在锁定区域爆发，余焰持续灼烧</x:v>
       </x:c>
       <x:c r="D24" t="n">
@@ -2214,14 +2217,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
+    <x:row r="25" ht="32" customHeight="1">
       <x:c r="A25" t="str">
         <x:v>SunBrand</x:v>
       </x:c>
-      <x:c r="B25" t="str">
+      <x:c r="B25" s="1" t="str">
         <x:v>烈阳烙印</x:v>
       </x:c>
-      <x:c r="C25" t="str">
+      <x:c r="C25" s="1" t="str">
         <x:v>三枚太阳烙印灼烧目标，移开标记格</x:v>
       </x:c>
       <x:c r="D25" t="n">
@@ -2264,14 +2267,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
+    <x:row r="26" ht="32" customHeight="1">
       <x:c r="A26" t="str">
         <x:v>TidalSurge</x:v>
       </x:c>
-      <x:c r="B26" t="str">
+      <x:c r="B26" s="1" t="str">
         <x:v>怒涛横卷</x:v>
       </x:c>
-      <x:c r="C26" t="str">
+      <x:c r="C26" s="1" t="str">
         <x:v>潮墙横扫一排，将棋子冲向侧方空格</x:v>
       </x:c>
       <x:c r="D26" t="n">
@@ -2314,14 +2317,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
+    <x:row r="27" ht="32" customHeight="1">
       <x:c r="A27" t="str">
         <x:v>Maelstrom</x:v>
       </x:c>
-      <x:c r="B27" t="str">
+      <x:c r="B27" s="1" t="str">
         <x:v>回流涡旋</x:v>
       </x:c>
-      <x:c r="C27" t="str">
+      <x:c r="C27" s="1" t="str">
         <x:v>旋流打乱中心阵型，远离旋涡区域</x:v>
       </x:c>
       <x:c r="D27" t="n">
@@ -2364,14 +2367,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
+    <x:row r="28" ht="32" customHeight="1">
       <x:c r="A28" t="str">
         <x:v>SwampMaw</x:v>
       </x:c>
-      <x:c r="B28" t="str">
+      <x:c r="B28" s="1" t="str">
         <x:v>沼泽巨口</x:v>
       </x:c>
-      <x:c r="C28" t="str">
+      <x:c r="C28" s="1" t="str">
         <x:v>沼泽暂时吞没局部阵型，随后吐回棋盘</x:v>
       </x:c>
       <x:c r="D28" t="n">
@@ -2414,14 +2417,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
+    <x:row r="29" ht="32" customHeight="1">
       <x:c r="A29" t="str">
         <x:v>MireChains</x:v>
       </x:c>
-      <x:c r="B29" t="str">
+      <x:c r="B29" s="1" t="str">
         <x:v>泥沼缚射</x:v>
       </x:c>
-      <x:c r="C29" t="str">
+      <x:c r="C29" s="1" t="str">
         <x:v>泥沼缠住区域内远程棋子，离开可解除减速</x:v>
       </x:c>
       <x:c r="D29" t="n">
@@ -2464,14 +2467,14 @@
         <x:v>0.45</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
+    <x:row r="30" ht="32" customHeight="1">
       <x:c r="A30" t="str">
         <x:v>FrozenPrison</x:v>
       </x:c>
-      <x:c r="B30" t="str">
+      <x:c r="B30" s="1" t="str">
         <x:v>极寒囚笼</x:v>
       </x:c>
-      <x:c r="C30" t="str">
+      <x:c r="C30" s="1" t="str">
         <x:v>冰晶冻结区域棋子两秒，期间无法攻击</x:v>
       </x:c>
       <x:c r="D30" t="n">
@@ -2514,14 +2517,14 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
+    <x:row r="31" ht="32" customHeight="1">
       <x:c r="A31" t="str">
         <x:v>GlacialAegis</x:v>
       </x:c>
-      <x:c r="B31" t="str">
+      <x:c r="B31" s="1" t="str">
         <x:v>冰封终焉</x:v>
       </x:c>
-      <x:c r="C31" t="str">
+      <x:c r="C31" s="1" t="str">
         <x:v>主将冰封无敌蓄能，冰壳碎裂时全盘爆炸</x:v>
       </x:c>
       <x:c r="D31" t="n">
@@ -2564,14 +2567,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="32" customHeight="1">
       <x:c r="A32" t="str">
         <x:v>DivineCross</x:v>
       </x:c>
-      <x:c r="B32" t="str">
+      <x:c r="B32" s="1" t="str">
         <x:v>十字神罚</x:v>
       </x:c>
-      <x:c r="C32" t="str">
+      <x:c r="C32" s="1" t="str">
         <x:v>金色十字将爆炸，避开横纵交会区域</x:v>
       </x:c>
       <x:c r="D32" t="n">
@@ -2614,14 +2617,14 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
+    <x:row r="33" ht="32" customHeight="1">
       <x:c r="A33" t="str">
         <x:v>Sanctuary</x:v>
       </x:c>
-      <x:c r="B33" t="str">
+      <x:c r="B33" s="1" t="str">
         <x:v>圣域</x:v>
       </x:c>
-      <x:c r="C33" t="str">
+      <x:c r="C33" s="1" t="str">
         <x:v>离开圣域恢复攻击与攻速，领域消退同时解除</x:v>
       </x:c>
       <x:c r="D33" t="n">
@@ -2661,6 +2664,1556 @@
         <x:v>0.65</x:v>
       </x:c>
       <x:c r="P33" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="32" customHeight="1">
+      <x:c r="A34" t="str">
+        <x:v>CometRails</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="str">
+        <x:v>彗星轨道</x:v>
+      </x:c>
+      <x:c r="C34" s="1" t="str">
+        <x:v>离开亮起的横纵交叉线</x:v>
+      </x:c>
+      <x:c r="D34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F34" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G34" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H34" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I34" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J34" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="K34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P34" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="32" customHeight="1">
+      <x:c r="A35" t="str">
+        <x:v>AstralShards</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="str">
+        <x:v>星屑追爆</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="str">
+        <x:v>三处落点已锁定，移出标记格</x:v>
+      </x:c>
+      <x:c r="D35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F35" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G35" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H35" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I35" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J35" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P35" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="32" customHeight="1">
+      <x:c r="A36" t="str">
+        <x:v>SolarSpears</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="str">
+        <x:v>烈阳贯枪</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="str">
+        <x:v>避开预警纵列，侧移至空列</x:v>
+      </x:c>
+      <x:c r="D36" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E36" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F36" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G36" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H36" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I36" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J36" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P36" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="32" customHeight="1">
+      <x:c r="A37" t="str">
+        <x:v>EmberFan</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="str">
+        <x:v>炎羽扇扫</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="str">
+        <x:v>离开扇区，退向未亮起的一侧</x:v>
+      </x:c>
+      <x:c r="D37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E37" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F37" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G37" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H37" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I37" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J37" t="n">
+        <x:v>0.52</x:v>
+      </x:c>
+      <x:c r="K37" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P37" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="32" customHeight="1">
+      <x:c r="A38" t="str">
+        <x:v>MagmaRings</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="str">
+        <x:v>熔岩环爆</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="str">
+        <x:v>环形冲击向外推进，站到未亮起的内外圈</x:v>
+      </x:c>
+      <x:c r="D38" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E38" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F38" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G38" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H38" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I38" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J38" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P38" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="32" customHeight="1">
+      <x:c r="A39" t="str">
+        <x:v>TidalLances</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="str">
+        <x:v>潮汐水枪</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="str">
+        <x:v>避开预警横排，移至空排</x:v>
+      </x:c>
+      <x:c r="D39" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E39" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F39" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I39" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J39" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P39" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="32" customHeight="1">
+      <x:c r="A40" t="str">
+        <x:v>FoamBurst</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="str">
+        <x:v>泡沫连爆</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="str">
+        <x:v>三处落点已锁定，移出标记格</x:v>
+      </x:c>
+      <x:c r="D40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E40" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F40" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G40" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H40" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I40" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J40" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P40" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="32" customHeight="1">
+      <x:c r="A41" t="str">
+        <x:v>Undertow</x:v>
+      </x:c>
+      <x:c r="B41" s="1" t="str">
+        <x:v>暗流绞阵</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="str">
+        <x:v>棋纹交替爆发，移向当前未亮的格</x:v>
+      </x:c>
+      <x:c r="D41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E41" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F41" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G41" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H41" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J41" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="K41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L41" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M41" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N41" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P41" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="32" customHeight="1">
+      <x:c r="A42" t="str">
+        <x:v>ReefSpikes</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="str">
+        <x:v>礁岩穿刺</x:v>
+      </x:c>
+      <x:c r="C42" s="1" t="str">
+        <x:v>离开冰晶或礁岩的对角裂线</x:v>
+      </x:c>
+      <x:c r="D42" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E42" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F42" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J42" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P42" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="32" customHeight="1">
+      <x:c r="A43" t="str">
+        <x:v>BogSpines</x:v>
+      </x:c>
+      <x:c r="B43" s="1" t="str">
+        <x:v>腐沼骨刺</x:v>
+      </x:c>
+      <x:c r="C43" s="1" t="str">
+        <x:v>避开预警纵列，侧移至空列</x:v>
+      </x:c>
+      <x:c r="D43" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E43" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F43" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G43" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H43" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I43" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J43" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="32" customHeight="1">
+      <x:c r="A44" t="str">
+        <x:v>VenomFan</x:v>
+      </x:c>
+      <x:c r="B44" s="1" t="str">
+        <x:v>毒雾扇潮</x:v>
+      </x:c>
+      <x:c r="C44" s="1" t="str">
+        <x:v>离开扇区，退向未亮起的一侧</x:v>
+      </x:c>
+      <x:c r="D44" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E44" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F44" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I44" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J44" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="K44" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P44" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="32" customHeight="1">
+      <x:c r="A45" t="str">
+        <x:v>MireRipples</x:v>
+      </x:c>
+      <x:c r="B45" s="1" t="str">
+        <x:v>泥潭连震</x:v>
+      </x:c>
+      <x:c r="C45" s="1" t="str">
+        <x:v>环形冲击向外推进，站到未亮起的内外圈</x:v>
+      </x:c>
+      <x:c r="D45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E45" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F45" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G45" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H45" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I45" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J45" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="32" customHeight="1">
+      <x:c r="A46" t="str">
+        <x:v>BlightSeeds</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="str">
+        <x:v>疫种爆裂</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="str">
+        <x:v>三处落点已锁定，移出标记格</x:v>
+      </x:c>
+      <x:c r="D46" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E46" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G46" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J46" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P46" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="32" customHeight="1">
+      <x:c r="A47" t="str">
+        <x:v>SnowCross</x:v>
+      </x:c>
+      <x:c r="B47" s="1" t="str">
+        <x:v>寒霜十字</x:v>
+      </x:c>
+      <x:c r="C47" s="1" t="str">
+        <x:v>离开亮起的横纵交叉线</x:v>
+      </x:c>
+      <x:c r="D47" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E47" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F47" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J47" t="n">
+        <x:v>0.9</x:v>
+      </x:c>
+      <x:c r="K47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="32" customHeight="1">
+      <x:c r="A48" t="str">
+        <x:v>HailBarrage</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="str">
+        <x:v>冰雹连坠</x:v>
+      </x:c>
+      <x:c r="C48" s="1" t="str">
+        <x:v>三处落点已锁定，移出标记格</x:v>
+      </x:c>
+      <x:c r="D48" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E48" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F48" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G48" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H48" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I48" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J48" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K48" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O48" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P48" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="32" customHeight="1">
+      <x:c r="A49" t="str">
+        <x:v>IceFault</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="str">
+        <x:v>冰川断层</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="str">
+        <x:v>离开冰晶或礁岩的对角裂线</x:v>
+      </x:c>
+      <x:c r="D49" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E49" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F49" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G49" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H49" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I49" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J49" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="K49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="32" customHeight="1">
+      <x:c r="A50" t="str">
+        <x:v>JudgementLances</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="str">
+        <x:v>裁决光矛</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="str">
+        <x:v>避开预警纵列，侧移至空列</x:v>
+      </x:c>
+      <x:c r="D50" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E50" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F50" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G50" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H50" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I50" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J50" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="32" customHeight="1">
+      <x:c r="A51" t="str">
+        <x:v>HaloPulse</x:v>
+      </x:c>
+      <x:c r="B51" s="1" t="str">
+        <x:v>圣环脉冲</x:v>
+      </x:c>
+      <x:c r="C51" s="1" t="str">
+        <x:v>环形冲击向外推进，站到未亮起的内外圈</x:v>
+      </x:c>
+      <x:c r="D51" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E51" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F51" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G51" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H51" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I51" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J51" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="32" customHeight="1">
+      <x:c r="A52" t="str">
+        <x:v>RunicGrid</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="str">
+        <x:v>律令棋阵</x:v>
+      </x:c>
+      <x:c r="C52" s="1" t="str">
+        <x:v>棋纹交替爆发，移向当前未亮的格</x:v>
+      </x:c>
+      <x:c r="D52" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E52" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F52" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G52" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="H52" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I52" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J52" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="K52" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="32" customHeight="1">
+      <x:c r="A53" t="str">
+        <x:v>EventHorizon</x:v>
+      </x:c>
+      <x:c r="B53" s="1" t="str">
+        <x:v>星界崩塌</x:v>
+      </x:c>
+      <x:c r="C53" s="1" t="str">
+        <x:v>引力环向内坍缩，退向外侧安全区</x:v>
+      </x:c>
+      <x:c r="D53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E53" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F53" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G53" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H53" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I53" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J53" t="n">
+        <x:v>0.38</x:v>
+      </x:c>
+      <x:c r="K53" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L53" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N53" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P53" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="32" customHeight="1">
+      <x:c r="A54" t="str">
+        <x:v>ConstellationSeal</x:v>
+      </x:c>
+      <x:c r="B54" s="1" t="str">
+        <x:v>星座封阵</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="str">
+        <x:v>避开横纵和对角星纹，站到星纹间隙</x:v>
+      </x:c>
+      <x:c r="D54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E54" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F54" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G54" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H54" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I54" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J54" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="K54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P54" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="32" customHeight="1">
+      <x:c r="A55" t="str">
+        <x:v>PhoenixDescent</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="str">
+        <x:v>焚天凤陨</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="str">
+        <x:v>三处落点已锁定，移出标记格</x:v>
+      </x:c>
+      <x:c r="D55" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E55" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F55" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G55" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H55" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I55" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J55" t="n">
+        <x:v>0.42</x:v>
+      </x:c>
+      <x:c r="K55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M55" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P55" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="32" customHeight="1">
+      <x:c r="A56" t="str">
+        <x:v>SolarEclipse</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="str">
+        <x:v>日蚀审判</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="str">
+        <x:v>日蚀环外扩，靠近未亮起的内圈</x:v>
+      </x:c>
+      <x:c r="D56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E56" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F56" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G56" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H56" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J56" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="K56" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M56" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P56" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="32" customHeight="1">
+      <x:c r="A57" t="str">
+        <x:v>LeviathanWake</x:v>
+      </x:c>
+      <x:c r="B57" s="1" t="str">
+        <x:v>巨鲸破浪</x:v>
+      </x:c>
+      <x:c r="C57" s="1" t="str">
+        <x:v>避开预警横排，移至空排</x:v>
+      </x:c>
+      <x:c r="D57" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E57" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F57" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G57" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H57" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I57" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J57" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="K57" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L57" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M57" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N57" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O57" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P57" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="32" customHeight="1">
+      <x:c r="A58" t="str">
+        <x:v>AbyssalCage</x:v>
+      </x:c>
+      <x:c r="B58" s="1" t="str">
+        <x:v>深渊潮牢</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="str">
+        <x:v>避开囚笼边框，后续离开整个区域</x:v>
+      </x:c>
+      <x:c r="D58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E58" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F58" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G58" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H58" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J58" t="n">
+        <x:v>0.48</x:v>
+      </x:c>
+      <x:c r="K58" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N58" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O58" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="P58" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="32" customHeight="1">
+      <x:c r="A59" t="str">
+        <x:v>PlagueBloom</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="str">
+        <x:v>瘟疫绽放</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="str">
+        <x:v>棋纹交替爆发，移向当前未亮的格</x:v>
+      </x:c>
+      <x:c r="D59" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E59" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F59" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G59" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H59" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I59" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J59" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K59" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M59" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N59" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O59" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="P59" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="32" customHeight="1">
+      <x:c r="A60" t="str">
+        <x:v>HydraFangs</x:v>
+      </x:c>
+      <x:c r="B60" s="1" t="str">
+        <x:v>九首獠牙</x:v>
+      </x:c>
+      <x:c r="C60" s="1" t="str">
+        <x:v>避开横纵和对角星纹，站到星纹间隙</x:v>
+      </x:c>
+      <x:c r="D60" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E60" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F60" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G60" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H60" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I60" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J60" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="K60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M60" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P60" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="32" customHeight="1">
+      <x:c r="A61" t="str">
+        <x:v>AbsoluteZero</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="str">
+        <x:v>绝对零域</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="str">
+        <x:v>避开囚笼边框，后续离开整个区域</x:v>
+      </x:c>
+      <x:c r="D61" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E61" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F61" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G61" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J61" t="n">
+        <x:v>0.3</x:v>
+      </x:c>
+      <x:c r="K61" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M61" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N61" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="O61" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="32" customHeight="1">
+      <x:c r="A62" t="str">
+        <x:v>Avalanche</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="str">
+        <x:v>万仞雪崩</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="str">
+        <x:v>避开预警横排，移至空排</x:v>
+      </x:c>
+      <x:c r="D62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E62" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F62" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G62" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H62" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I62" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J62" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="K62" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L62" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M62" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N62" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O62" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P62" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="32" customHeight="1">
+      <x:c r="A63" t="str">
+        <x:v>Heavenfall</x:v>
+      </x:c>
+      <x:c r="B63" s="1" t="str">
+        <x:v>天穹裁决</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="str">
+        <x:v>避开横纵和对角星纹，站到星纹间隙</x:v>
+      </x:c>
+      <x:c r="D63" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E63" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F63" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G63" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H63" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I63" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J63" t="n">
+        <x:v>0.52</x:v>
+      </x:c>
+      <x:c r="K63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M63" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="32" customHeight="1">
+      <x:c r="A64" t="str">
+        <x:v>FinalEdict</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="str">
+        <x:v>终极律令</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="str">
+        <x:v>棋纹交替爆发，移向当前未亮的格</x:v>
+      </x:c>
+      <x:c r="D64" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E64" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F64" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G64" t="n">
+        <x:v>1.7</x:v>
+      </x:c>
+      <x:c r="H64" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="I64" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J64" t="n">
+        <x:v>0.32</x:v>
+      </x:c>
+      <x:c r="K64" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="L64" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M64" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N64" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="O64" t="n">
+        <x:v>0.75</x:v>
+      </x:c>
+      <x:c r="P64" t="n">
         <x:v>0.55</x:v>
       </x:c>
     </x:row>
